--- a/Notes/sample.xlsx
+++ b/Notes/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jane\Documents\Project 2\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D4CC95-B849-478F-B431-FFE868518774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9B543E-DE16-47B3-A26B-F666FA002B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E6CF6E38-6E12-4D14-921E-BC8F3EA0613E}"/>
   </bookViews>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>__rowid__</t>
   </si>
@@ -69,33 +91,6 @@
     <t>ave</t>
   </si>
   <si>
-    <t>12.9</t>
-  </si>
-  <si>
-    <t>9.4</t>
-  </si>
-  <si>
-    <t>31.5</t>
-  </si>
-  <si>
-    <t>83.2</t>
-  </si>
-  <si>
-    <t>21.3</t>
-  </si>
-  <si>
-    <t>44.3</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>1926.0</t>
-  </si>
-  <si>
-    <t>259.7</t>
-  </si>
-  <si>
     <t>temp001</t>
   </si>
   <si>
@@ -107,13 +102,17 @@
   <si>
     <t>par004</t>
   </si>
+  <si>
+    <t>threshold</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -144,11 +143,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,51 +510,51 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
+      <c r="B2" s="2">
+        <v>12.9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>9.4</v>
       </c>
       <c r="D2" s="2">
         <v>16.5</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>16</v>
+      <c r="E2" s="4">
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
+      <c r="B3" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>83.2</v>
       </c>
       <c r="D3" s="2">
         <v>20.5</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
+      <c r="E3" s="4">
+        <v>1400</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
+      <c r="B4" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>44.3</v>
       </c>
       <c r="D4" s="2">
         <v>18.5</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
+      <c r="E4" s="4">
+        <v>1650</v>
       </c>
     </row>
   </sheetData>
@@ -564,7 +564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C450A4A-4ABB-4DB3-A056-8EA30DB7B11B}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
@@ -572,7 +572,7 @@
     <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -592,19 +592,22 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -623,12 +626,24 @@
       <c r="F2" s="3">
         <v>1546</v>
       </c>
-      <c r="G2" t="str">
-        <f>IF(C2&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G2" cm="1">
+        <f t="array" aca="1" ref="G2" ca="1">IF(C2&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C2&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H2" cm="1">
+        <f t="array" aca="1" ref="H2" ca="1">IF(D2&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D2&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I2" cm="1">
+        <f t="array" aca="1" ref="I2" ca="1">IF(E2&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E2&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J2" cm="1">
+        <f t="array" aca="1" ref="J2" ca="1">IF(F2&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F2&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -647,12 +662,24 @@
       <c r="F3" s="3">
         <v>1417</v>
       </c>
-      <c r="G3" t="str">
-        <f>IF(C3&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G3" cm="1">
+        <f t="array" aca="1" ref="G3" ca="1">IF(C3&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C3&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H3" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">IF(D3&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D3&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I3" cm="1">
+        <f t="array" aca="1" ref="I3" ca="1">IF(E3&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E3&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J3" cm="1">
+        <f t="array" aca="1" ref="J3" ca="1">IF(F3&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F3&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -671,12 +698,24 @@
       <c r="F4" s="3">
         <v>1462</v>
       </c>
-      <c r="G4" t="str">
-        <f>IF(C4&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G4" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">IF(C4&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C4&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H4" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">IF(D4&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D4&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I4" cm="1">
+        <f t="array" aca="1" ref="I4" ca="1">IF(E4&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E4&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J4" cm="1">
+        <f t="array" aca="1" ref="J4" ca="1">IF(F4&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F4&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -695,12 +734,24 @@
       <c r="F5" s="3">
         <v>1838</v>
       </c>
-      <c r="G5" t="str">
-        <f>IF(C5&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G5" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">IF(C5&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C5&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H5" cm="1">
+        <f t="array" aca="1" ref="H5" ca="1">IF(D5&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D5&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I5" cm="1">
+        <f t="array" aca="1" ref="I5" ca="1">IF(E5&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E5&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J5" cm="1">
+        <f t="array" aca="1" ref="J5" ca="1">IF(F5&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F5&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -719,12 +770,24 @@
       <c r="F6" s="3">
         <v>114</v>
       </c>
-      <c r="G6" t="str">
-        <f>IF(C6&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G6" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">IF(C6&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C6&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H6" cm="1">
+        <f t="array" aca="1" ref="H6" ca="1">IF(D6&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D6&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I6" cm="1">
+        <f t="array" aca="1" ref="I6" ca="1">IF(E6&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E6&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J6" cm="1">
+        <f t="array" aca="1" ref="J6" ca="1">IF(F6&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F6&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -743,12 +806,24 @@
       <c r="F7" s="3">
         <v>2080</v>
       </c>
-      <c r="G7" t="str">
-        <f>IF(C7&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G7" cm="1">
+        <f t="array" aca="1" ref="G7" ca="1">IF(C7&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C7&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H7" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">IF(D7&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D7&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I7" cm="1">
+        <f t="array" aca="1" ref="I7" ca="1">IF(E7&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E7&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J7" cm="1">
+        <f t="array" aca="1" ref="J7" ca="1">IF(F7&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F7&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -767,12 +842,24 @@
       <c r="F8" s="3">
         <v>1176</v>
       </c>
-      <c r="G8" t="str">
-        <f>IF(C8&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G8" cm="1">
+        <f t="array" aca="1" ref="G8" ca="1">IF(C8&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C8&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H8" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">IF(D8&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D8&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I8" cm="1">
+        <f t="array" aca="1" ref="I8" ca="1">IF(E8&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E8&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J8" cm="1">
+        <f t="array" aca="1" ref="J8" ca="1">IF(F8&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F8&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -791,12 +878,24 @@
       <c r="F9" s="3">
         <v>731</v>
       </c>
-      <c r="G9" t="str">
-        <f>IF(C9&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G9" cm="1">
+        <f t="array" aca="1" ref="G9" ca="1">IF(C9&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C9&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H9" cm="1">
+        <f t="array" aca="1" ref="H9" ca="1">IF(D9&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D9&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I9" cm="1">
+        <f t="array" aca="1" ref="I9" ca="1">IF(E9&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E9&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J9" cm="1">
+        <f t="array" aca="1" ref="J9" ca="1">IF(F9&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F9&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -815,12 +914,24 @@
       <c r="F10" s="3">
         <v>387</v>
       </c>
-      <c r="G10" t="str">
-        <f>IF(C10&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G10" cm="1">
+        <f t="array" aca="1" ref="G10" ca="1">IF(C10&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C10&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H10" cm="1">
+        <f t="array" aca="1" ref="H10" ca="1">IF(D10&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D10&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I10" cm="1">
+        <f t="array" aca="1" ref="I10" ca="1">IF(E10&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E10&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J10" cm="1">
+        <f t="array" aca="1" ref="J10" ca="1">IF(F10&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F10&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -839,12 +950,24 @@
       <c r="F11" s="3">
         <v>1529</v>
       </c>
-      <c r="G11" t="str">
-        <f>IF(C11&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G11" cm="1">
+        <f t="array" aca="1" ref="G11" ca="1">IF(C11&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C11&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H11" cm="1">
+        <f t="array" aca="1" ref="H11" ca="1">IF(D11&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D11&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I11" cm="1">
+        <f t="array" aca="1" ref="I11" ca="1">IF(E11&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E11&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J11" cm="1">
+        <f t="array" aca="1" ref="J11" ca="1">IF(F11&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F11&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -863,12 +986,24 @@
       <c r="F12" s="3">
         <v>1141</v>
       </c>
-      <c r="G12" t="str">
-        <f>IF(C12&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G12" cm="1">
+        <f t="array" aca="1" ref="G12" ca="1">IF(C12&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C12&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H12" cm="1">
+        <f t="array" aca="1" ref="H12" ca="1">IF(D12&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D12&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="I12" cm="1">
+        <f t="array" aca="1" ref="I12" ca="1">IF(E12&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E12&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J12" cm="1">
+        <f t="array" aca="1" ref="J12" ca="1">IF(F12&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F12&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -887,12 +1022,24 @@
       <c r="F13" s="3">
         <v>231</v>
       </c>
-      <c r="G13" t="str">
-        <f>IF(C13&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G13" cm="1">
+        <f t="array" aca="1" ref="G13" ca="1">IF(C13&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C13&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H13" cm="1">
+        <f t="array" aca="1" ref="H13" ca="1">IF(D13&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D13&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I13" cm="1">
+        <f t="array" aca="1" ref="I13" ca="1">IF(E13&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E13&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J13" cm="1">
+        <f t="array" aca="1" ref="J13" ca="1">IF(F13&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F13&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -911,12 +1058,24 @@
       <c r="F14" s="3">
         <v>305</v>
       </c>
-      <c r="G14" t="str">
-        <f>IF(C14&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G14" cm="1">
+        <f t="array" aca="1" ref="G14" ca="1">IF(C14&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C14&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H14" cm="1">
+        <f t="array" aca="1" ref="H14" ca="1">IF(D14&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D14&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I14" cm="1">
+        <f t="array" aca="1" ref="I14" ca="1">IF(E14&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E14&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J14" cm="1">
+        <f t="array" aca="1" ref="J14" ca="1">IF(F14&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F14&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -935,12 +1094,24 @@
       <c r="F15" s="3">
         <v>278</v>
       </c>
-      <c r="G15" t="str">
-        <f>IF(C15&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G15" cm="1">
+        <f t="array" aca="1" ref="G15" ca="1">IF(C15&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C15&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H15" cm="1">
+        <f t="array" aca="1" ref="H15" ca="1">IF(D15&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D15&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I15" cm="1">
+        <f t="array" aca="1" ref="I15" ca="1">IF(E15&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E15&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J15" cm="1">
+        <f t="array" aca="1" ref="J15" ca="1">IF(F15&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F15&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -959,12 +1130,24 @@
       <c r="F16" s="3">
         <v>1645</v>
       </c>
-      <c r="G16" t="str">
-        <f>IF(C16&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G16" cm="1">
+        <f t="array" aca="1" ref="G16" ca="1">IF(C16&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C16&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H16" cm="1">
+        <f t="array" aca="1" ref="H16" ca="1">IF(D16&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D16&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" cm="1">
+        <f t="array" aca="1" ref="I16" ca="1">IF(E16&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E16&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J16" cm="1">
+        <f t="array" aca="1" ref="J16" ca="1">IF(F16&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F16&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -983,12 +1166,24 @@
       <c r="F17" s="3">
         <v>991</v>
       </c>
-      <c r="G17" t="str">
-        <f>IF(C17&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G17" cm="1">
+        <f t="array" aca="1" ref="G17" ca="1">IF(C17&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C17&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H17" cm="1">
+        <f t="array" aca="1" ref="H17" ca="1">IF(D17&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D17&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I17" cm="1">
+        <f t="array" aca="1" ref="I17" ca="1">IF(E17&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E17&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J17" cm="1">
+        <f t="array" aca="1" ref="J17" ca="1">IF(F17&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F17&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1007,12 +1202,24 @@
       <c r="F18" s="3">
         <v>2281</v>
       </c>
-      <c r="G18" t="str">
-        <f>IF(C18&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G18" cm="1">
+        <f t="array" aca="1" ref="G18" ca="1">IF(C18&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C18&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H18" cm="1">
+        <f t="array" aca="1" ref="H18" ca="1">IF(D18&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D18&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I18" cm="1">
+        <f t="array" aca="1" ref="I18" ca="1">IF(E18&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E18&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J18" cm="1">
+        <f t="array" aca="1" ref="J18" ca="1">IF(F18&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F18&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1031,12 +1238,24 @@
       <c r="F19" s="3">
         <v>2177</v>
       </c>
-      <c r="G19" t="str">
-        <f>IF(C19&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G19" cm="1">
+        <f t="array" aca="1" ref="G19" ca="1">IF(C19&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C19&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H19" cm="1">
+        <f t="array" aca="1" ref="H19" ca="1">IF(D19&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D19&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I19" cm="1">
+        <f t="array" aca="1" ref="I19" ca="1">IF(E19&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E19&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J19" cm="1">
+        <f t="array" aca="1" ref="J19" ca="1">IF(F19&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F19&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1055,12 +1274,24 @@
       <c r="F20" s="3">
         <v>2087</v>
       </c>
-      <c r="G20" t="str">
-        <f>IF(C20&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G20" cm="1">
+        <f t="array" aca="1" ref="G20" ca="1">IF(C20&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C20&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H20" cm="1">
+        <f t="array" aca="1" ref="H20" ca="1">IF(D20&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D20&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I20" cm="1">
+        <f t="array" aca="1" ref="I20" ca="1">IF(E20&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E20&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J20" cm="1">
+        <f t="array" aca="1" ref="J20" ca="1">IF(F20&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F20&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1079,12 +1310,24 @@
       <c r="F21" s="3">
         <v>1321</v>
       </c>
-      <c r="G21" t="str">
-        <f>IF(C21&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G21" cm="1">
+        <f t="array" aca="1" ref="G21" ca="1">IF(C21&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C21&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H21" cm="1">
+        <f t="array" aca="1" ref="H21" ca="1">IF(D21&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D21&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I21" cm="1">
+        <f t="array" aca="1" ref="I21" ca="1">IF(E21&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E21&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J21" cm="1">
+        <f t="array" aca="1" ref="J21" ca="1">IF(F21&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F21&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1103,12 +1346,24 @@
       <c r="F22" s="3">
         <v>1622</v>
       </c>
-      <c r="G22" t="str">
-        <f>IF(C22&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G22" cm="1">
+        <f t="array" aca="1" ref="G22" ca="1">IF(C22&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C22&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H22" cm="1">
+        <f t="array" aca="1" ref="H22" ca="1">IF(D22&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D22&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I22" cm="1">
+        <f t="array" aca="1" ref="I22" ca="1">IF(E22&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E22&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J22" cm="1">
+        <f t="array" aca="1" ref="J22" ca="1">IF(F22&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F22&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1127,12 +1382,24 @@
       <c r="F23" s="3">
         <v>776</v>
       </c>
-      <c r="G23" t="str">
-        <f>IF(C23&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G23" cm="1">
+        <f t="array" aca="1" ref="G23" ca="1">IF(C23&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C23&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H23" cm="1">
+        <f t="array" aca="1" ref="H23" ca="1">IF(D23&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D23&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I23" cm="1">
+        <f t="array" aca="1" ref="I23" ca="1">IF(E23&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E23&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J23" cm="1">
+        <f t="array" aca="1" ref="J23" ca="1">IF(F23&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F23&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1151,12 +1418,24 @@
       <c r="F24" s="3">
         <v>1563</v>
       </c>
-      <c r="G24" t="str">
-        <f>IF(C24&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G24" cm="1">
+        <f t="array" aca="1" ref="G24" ca="1">IF(C24&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C24&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H24" cm="1">
+        <f t="array" aca="1" ref="H24" ca="1">IF(D24&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D24&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I24" cm="1">
+        <f t="array" aca="1" ref="I24" ca="1">IF(E24&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E24&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J24" cm="1">
+        <f t="array" aca="1" ref="J24" ca="1">IF(F24&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F24&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1175,12 +1454,24 @@
       <c r="F25" s="3">
         <v>1740</v>
       </c>
-      <c r="G25" t="str">
-        <f>IF(C25&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G25" cm="1">
+        <f t="array" aca="1" ref="G25" ca="1">IF(C25&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C25&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H25" cm="1">
+        <f t="array" aca="1" ref="H25" ca="1">IF(D25&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D25&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I25" cm="1">
+        <f t="array" aca="1" ref="I25" ca="1">IF(E25&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E25&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J25" cm="1">
+        <f t="array" aca="1" ref="J25" ca="1">IF(F25&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F25&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1199,12 +1490,24 @@
       <c r="F26" s="3">
         <v>858</v>
       </c>
-      <c r="G26" t="str">
-        <f>IF(C26&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G26" cm="1">
+        <f t="array" aca="1" ref="G26" ca="1">IF(C26&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C26&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H26" cm="1">
+        <f t="array" aca="1" ref="H26" ca="1">IF(D26&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D26&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I26" cm="1">
+        <f t="array" aca="1" ref="I26" ca="1">IF(E26&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E26&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J26" cm="1">
+        <f t="array" aca="1" ref="J26" ca="1">IF(F26&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F26&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1223,12 +1526,24 @@
       <c r="F27" s="3">
         <v>1316</v>
       </c>
-      <c r="G27" t="str">
-        <f>IF(C27&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G27" cm="1">
+        <f t="array" aca="1" ref="G27" ca="1">IF(C27&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C27&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H27" cm="1">
+        <f t="array" aca="1" ref="H27" ca="1">IF(D27&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D27&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I27" cm="1">
+        <f t="array" aca="1" ref="I27" ca="1">IF(E27&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E27&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J27" cm="1">
+        <f t="array" aca="1" ref="J27" ca="1">IF(F27&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F27&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1247,12 +1562,24 @@
       <c r="F28" s="3">
         <v>401</v>
       </c>
-      <c r="G28" t="str">
-        <f>IF(C28&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G28" cm="1">
+        <f t="array" aca="1" ref="G28" ca="1">IF(C28&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C28&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H28" cm="1">
+        <f t="array" aca="1" ref="H28" ca="1">IF(D28&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D28&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I28" cm="1">
+        <f t="array" aca="1" ref="I28" ca="1">IF(E28&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E28&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J28" cm="1">
+        <f t="array" aca="1" ref="J28" ca="1">IF(F28&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F28&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1271,12 +1598,24 @@
       <c r="F29" s="3">
         <v>1760</v>
       </c>
-      <c r="G29" t="str">
-        <f>IF(C29&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G29" cm="1">
+        <f t="array" aca="1" ref="G29" ca="1">IF(C29&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C29&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H29" cm="1">
+        <f t="array" aca="1" ref="H29" ca="1">IF(D29&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D29&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I29" cm="1">
+        <f t="array" aca="1" ref="I29" ca="1">IF(E29&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E29&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J29" cm="1">
+        <f t="array" aca="1" ref="J29" ca="1">IF(F29&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F29&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1295,12 +1634,24 @@
       <c r="F30" s="3">
         <v>674</v>
       </c>
-      <c r="G30" t="str">
-        <f>IF(C30&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G30" cm="1">
+        <f t="array" aca="1" ref="G30" ca="1">IF(C30&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C30&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H30" cm="1">
+        <f t="array" aca="1" ref="H30" ca="1">IF(D30&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D30&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I30" cm="1">
+        <f t="array" aca="1" ref="I30" ca="1">IF(E30&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E30&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J30" cm="1">
+        <f t="array" aca="1" ref="J30" ca="1">IF(F30&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F30&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1319,12 +1670,24 @@
       <c r="F31" s="3">
         <v>1332</v>
       </c>
-      <c r="G31" t="str">
-        <f>IF(C31&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G31" cm="1">
+        <f t="array" aca="1" ref="G31" ca="1">IF(C31&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C31&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H31" cm="1">
+        <f t="array" aca="1" ref="H31" ca="1">IF(D31&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D31&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I31" cm="1">
+        <f t="array" aca="1" ref="I31" ca="1">IF(E31&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E31&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J31" cm="1">
+        <f t="array" aca="1" ref="J31" ca="1">IF(F31&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F31&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1343,12 +1706,24 @@
       <c r="F32" s="3">
         <v>2140</v>
       </c>
-      <c r="G32" t="str">
-        <f>IF(C32&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G32" cm="1">
+        <f t="array" aca="1" ref="G32" ca="1">IF(C32&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C32&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H32" cm="1">
+        <f t="array" aca="1" ref="H32" ca="1">IF(D32&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D32&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I32" cm="1">
+        <f t="array" aca="1" ref="I32" ca="1">IF(E32&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E32&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J32" cm="1">
+        <f t="array" aca="1" ref="J32" ca="1">IF(F32&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F32&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1367,12 +1742,24 @@
       <c r="F33" s="3">
         <v>1597</v>
       </c>
-      <c r="G33" t="str">
-        <f>IF(C33&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33" cm="1">
+        <f t="array" aca="1" ref="G33" ca="1">IF(C33&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C33&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H33" cm="1">
+        <f t="array" aca="1" ref="H33" ca="1">IF(D33&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D33&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I33" cm="1">
+        <f t="array" aca="1" ref="I33" ca="1">IF(E33&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E33&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J33" cm="1">
+        <f t="array" aca="1" ref="J33" ca="1">IF(F33&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F33&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1391,12 +1778,24 @@
       <c r="F34" s="3">
         <v>1338</v>
       </c>
-      <c r="G34" t="str">
-        <f>IF(C34&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G34" cm="1">
+        <f t="array" aca="1" ref="G34" ca="1">IF(C34&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C34&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H34" cm="1">
+        <f t="array" aca="1" ref="H34" ca="1">IF(D34&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D34&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I34" cm="1">
+        <f t="array" aca="1" ref="I34" ca="1">IF(E34&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E34&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J34" cm="1">
+        <f t="array" aca="1" ref="J34" ca="1">IF(F34&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F34&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1415,12 +1814,24 @@
       <c r="F35" s="3">
         <v>1650</v>
       </c>
-      <c r="G35" t="str">
-        <f>IF(C35&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G35" cm="1">
+        <f t="array" aca="1" ref="G35" ca="1">IF(C35&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C35&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H35" cm="1">
+        <f t="array" aca="1" ref="H35" ca="1">IF(D35&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D35&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I35" cm="1">
+        <f t="array" aca="1" ref="I35" ca="1">IF(E35&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E35&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J35" cm="1">
+        <f t="array" aca="1" ref="J35" ca="1">IF(F35&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F35&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1439,12 +1850,24 @@
       <c r="F36" s="3">
         <v>551</v>
       </c>
-      <c r="G36" t="str">
-        <f>IF(C36&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G36" cm="1">
+        <f t="array" aca="1" ref="G36" ca="1">IF(C36&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C36&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H36" cm="1">
+        <f t="array" aca="1" ref="H36" ca="1">IF(D36&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D36&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I36" cm="1">
+        <f t="array" aca="1" ref="I36" ca="1">IF(E36&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E36&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J36" cm="1">
+        <f t="array" aca="1" ref="J36" ca="1">IF(F36&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F36&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1463,12 +1886,24 @@
       <c r="F37" s="3">
         <v>107</v>
       </c>
-      <c r="G37" t="str">
-        <f>IF(C37&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G37" cm="1">
+        <f t="array" aca="1" ref="G37" ca="1">IF(C37&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C37&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H37" cm="1">
+        <f t="array" aca="1" ref="H37" ca="1">IF(D37&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D37&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I37" cm="1">
+        <f t="array" aca="1" ref="I37" ca="1">IF(E37&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E37&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J37" cm="1">
+        <f t="array" aca="1" ref="J37" ca="1">IF(F37&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F37&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1487,12 +1922,24 @@
       <c r="F38" s="3">
         <v>2164</v>
       </c>
-      <c r="G38" t="str">
-        <f>IF(C38&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G38" cm="1">
+        <f t="array" aca="1" ref="G38" ca="1">IF(C38&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C38&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H38" cm="1">
+        <f t="array" aca="1" ref="H38" ca="1">IF(D38&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D38&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I38" cm="1">
+        <f t="array" aca="1" ref="I38" ca="1">IF(E38&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E38&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J38" cm="1">
+        <f t="array" aca="1" ref="J38" ca="1">IF(F38&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F38&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1511,12 +1958,24 @@
       <c r="F39" s="3">
         <v>1127</v>
       </c>
-      <c r="G39" t="str">
-        <f>IF(C39&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G39" cm="1">
+        <f t="array" aca="1" ref="G39" ca="1">IF(C39&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C39&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H39" cm="1">
+        <f t="array" aca="1" ref="H39" ca="1">IF(D39&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D39&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I39" cm="1">
+        <f t="array" aca="1" ref="I39" ca="1">IF(E39&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E39&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J39" cm="1">
+        <f t="array" aca="1" ref="J39" ca="1">IF(F39&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F39&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1535,12 +1994,24 @@
       <c r="F40" s="3">
         <v>2150</v>
       </c>
-      <c r="G40" t="str">
-        <f>IF(C40&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G40" cm="1">
+        <f t="array" aca="1" ref="G40" ca="1">IF(C40&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C40&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H40" cm="1">
+        <f t="array" aca="1" ref="H40" ca="1">IF(D40&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D40&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I40" cm="1">
+        <f t="array" aca="1" ref="I40" ca="1">IF(E40&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E40&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J40" cm="1">
+        <f t="array" aca="1" ref="J40" ca="1">IF(F40&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F40&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1559,12 +2030,24 @@
       <c r="F41" s="3">
         <v>1797</v>
       </c>
-      <c r="G41" t="str">
-        <f>IF(C41&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G41" cm="1">
+        <f t="array" aca="1" ref="G41" ca="1">IF(C41&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C41&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H41" cm="1">
+        <f t="array" aca="1" ref="H41" ca="1">IF(D41&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D41&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I41" cm="1">
+        <f t="array" aca="1" ref="I41" ca="1">IF(E41&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E41&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J41" cm="1">
+        <f t="array" aca="1" ref="J41" ca="1">IF(F41&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F41&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1583,12 +2066,24 @@
       <c r="F42" s="3">
         <v>465</v>
       </c>
-      <c r="G42" t="str">
-        <f>IF(C42&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G42" cm="1">
+        <f t="array" aca="1" ref="G42" ca="1">IF(C42&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C42&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H42" cm="1">
+        <f t="array" aca="1" ref="H42" ca="1">IF(D42&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D42&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I42" cm="1">
+        <f t="array" aca="1" ref="I42" ca="1">IF(E42&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E42&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J42" cm="1">
+        <f t="array" aca="1" ref="J42" ca="1">IF(F42&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F42&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1607,12 +2102,24 @@
       <c r="F43" s="3">
         <v>1557</v>
       </c>
-      <c r="G43" t="str">
-        <f>IF(C43&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G43" cm="1">
+        <f t="array" aca="1" ref="G43" ca="1">IF(C43&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C43&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H43" cm="1">
+        <f t="array" aca="1" ref="H43" ca="1">IF(D43&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D43&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I43" cm="1">
+        <f t="array" aca="1" ref="I43" ca="1">IF(E43&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E43&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J43" cm="1">
+        <f t="array" aca="1" ref="J43" ca="1">IF(F43&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F43&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1631,12 +2138,24 @@
       <c r="F44" s="3">
         <v>2154</v>
       </c>
-      <c r="G44" t="str">
-        <f>IF(C44&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G44" cm="1">
+        <f t="array" aca="1" ref="G44" ca="1">IF(C44&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C44&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H44" cm="1">
+        <f t="array" aca="1" ref="H44" ca="1">IF(D44&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D44&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I44" cm="1">
+        <f t="array" aca="1" ref="I44" ca="1">IF(E44&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E44&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J44" cm="1">
+        <f t="array" aca="1" ref="J44" ca="1">IF(F44&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F44&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1655,12 +2174,24 @@
       <c r="F45" s="3">
         <v>196</v>
       </c>
-      <c r="G45" t="str">
-        <f>IF(C45&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G45" cm="1">
+        <f t="array" aca="1" ref="G45" ca="1">IF(C45&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C45&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H45" cm="1">
+        <f t="array" aca="1" ref="H45" ca="1">IF(D45&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D45&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I45" cm="1">
+        <f t="array" aca="1" ref="I45" ca="1">IF(E45&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E45&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J45" cm="1">
+        <f t="array" aca="1" ref="J45" ca="1">IF(F45&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F45&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1679,12 +2210,24 @@
       <c r="F46" s="3">
         <v>536</v>
       </c>
-      <c r="G46" t="str">
-        <f>IF(C46&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G46" cm="1">
+        <f t="array" aca="1" ref="G46" ca="1">IF(C46&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C46&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H46" cm="1">
+        <f t="array" aca="1" ref="H46" ca="1">IF(D46&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D46&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I46" cm="1">
+        <f t="array" aca="1" ref="I46" ca="1">IF(E46&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E46&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J46" cm="1">
+        <f t="array" aca="1" ref="J46" ca="1">IF(F46&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F46&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1703,12 +2246,24 @@
       <c r="F47" s="3">
         <v>386</v>
       </c>
-      <c r="G47" t="str">
-        <f>IF(C47&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47" cm="1">
+        <f t="array" aca="1" ref="G47" ca="1">IF(C47&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C47&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H47" cm="1">
+        <f t="array" aca="1" ref="H47" ca="1">IF(D47&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D47&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I47" cm="1">
+        <f t="array" aca="1" ref="I47" ca="1">IF(E47&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E47&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J47" cm="1">
+        <f t="array" aca="1" ref="J47" ca="1">IF(F47&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F47&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1727,12 +2282,24 @@
       <c r="F48" s="3">
         <v>2212</v>
       </c>
-      <c r="G48" t="str">
-        <f>IF(C48&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G48" cm="1">
+        <f t="array" aca="1" ref="G48" ca="1">IF(C48&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C48&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H48" cm="1">
+        <f t="array" aca="1" ref="H48" ca="1">IF(D48&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D48&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I48" cm="1">
+        <f t="array" aca="1" ref="I48" ca="1">IF(E48&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E48&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J48" cm="1">
+        <f t="array" aca="1" ref="J48" ca="1">IF(F48&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F48&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1751,12 +2318,24 @@
       <c r="F49" s="3">
         <v>5</v>
       </c>
-      <c r="G49" t="str">
-        <f>IF(C49&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G49" cm="1">
+        <f t="array" aca="1" ref="G49" ca="1">IF(C49&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C49&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H49" cm="1">
+        <f t="array" aca="1" ref="H49" ca="1">IF(D49&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D49&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I49" cm="1">
+        <f t="array" aca="1" ref="I49" ca="1">IF(E49&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E49&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J49" cm="1">
+        <f t="array" aca="1" ref="J49" ca="1">IF(F49&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F49&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1775,12 +2354,24 @@
       <c r="F50" s="3">
         <v>453</v>
       </c>
-      <c r="G50" t="str">
-        <f>IF(C50&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G50" cm="1">
+        <f t="array" aca="1" ref="G50" ca="1">IF(C50&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C50&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H50" cm="1">
+        <f t="array" aca="1" ref="H50" ca="1">IF(D50&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D50&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="I50" cm="1">
+        <f t="array" aca="1" ref="I50" ca="1">IF(E50&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E50&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J50" cm="1">
+        <f t="array" aca="1" ref="J50" ca="1">IF(F50&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F50&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1799,12 +2390,24 @@
       <c r="F51" s="3">
         <v>439</v>
       </c>
-      <c r="G51" t="str">
-        <f>IF(C51&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G51" cm="1">
+        <f t="array" aca="1" ref="G51" ca="1">IF(C51&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C51&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H51" cm="1">
+        <f t="array" aca="1" ref="H51" ca="1">IF(D51&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D51&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I51" cm="1">
+        <f t="array" aca="1" ref="I51" ca="1">IF(E51&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E51&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J51" cm="1">
+        <f t="array" aca="1" ref="J51" ca="1">IF(F51&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F51&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1823,12 +2426,24 @@
       <c r="F52" s="3">
         <v>2195</v>
       </c>
-      <c r="G52" t="str">
-        <f>IF(C52&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G52" cm="1">
+        <f t="array" aca="1" ref="G52" ca="1">IF(C52&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C52&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H52" cm="1">
+        <f t="array" aca="1" ref="H52" ca="1">IF(D52&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D52&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I52" cm="1">
+        <f t="array" aca="1" ref="I52" ca="1">IF(E52&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E52&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J52" cm="1">
+        <f t="array" aca="1" ref="J52" ca="1">IF(F52&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F52&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1847,12 +2462,24 @@
       <c r="F53" s="3">
         <v>1482</v>
       </c>
-      <c r="G53" t="str">
-        <f>IF(C53&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G53" cm="1">
+        <f t="array" aca="1" ref="G53" ca="1">IF(C53&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C53&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H53" cm="1">
+        <f t="array" aca="1" ref="H53" ca="1">IF(D53&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D53&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I53" cm="1">
+        <f t="array" aca="1" ref="I53" ca="1">IF(E53&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E53&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J53" cm="1">
+        <f t="array" aca="1" ref="J53" ca="1">IF(F53&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F53&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1871,12 +2498,24 @@
       <c r="F54" s="3">
         <v>1487</v>
       </c>
-      <c r="G54" t="str">
-        <f>IF(C54&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G54" cm="1">
+        <f t="array" aca="1" ref="G54" ca="1">IF(C54&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C54&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H54" cm="1">
+        <f t="array" aca="1" ref="H54" ca="1">IF(D54&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D54&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I54" cm="1">
+        <f t="array" aca="1" ref="I54" ca="1">IF(E54&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E54&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J54" cm="1">
+        <f t="array" aca="1" ref="J54" ca="1">IF(F54&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F54&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1895,12 +2534,24 @@
       <c r="F55" s="3">
         <v>294</v>
       </c>
-      <c r="G55" t="str">
-        <f>IF(C55&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G55" cm="1">
+        <f t="array" aca="1" ref="G55" ca="1">IF(C55&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C55&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H55" cm="1">
+        <f t="array" aca="1" ref="H55" ca="1">IF(D55&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D55&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I55" cm="1">
+        <f t="array" aca="1" ref="I55" ca="1">IF(E55&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E55&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J55" cm="1">
+        <f t="array" aca="1" ref="J55" ca="1">IF(F55&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F55&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1919,12 +2570,24 @@
       <c r="F56" s="3">
         <v>1313</v>
       </c>
-      <c r="G56" t="str">
-        <f>IF(C56&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G56" cm="1">
+        <f t="array" aca="1" ref="G56" ca="1">IF(C56&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C56&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H56" cm="1">
+        <f t="array" aca="1" ref="H56" ca="1">IF(D56&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D56&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I56" cm="1">
+        <f t="array" aca="1" ref="I56" ca="1">IF(E56&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E56&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J56" cm="1">
+        <f t="array" aca="1" ref="J56" ca="1">IF(F56&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F56&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1943,12 +2606,24 @@
       <c r="F57" s="3">
         <v>1758</v>
       </c>
-      <c r="G57" t="str">
-        <f>IF(C57&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G57" cm="1">
+        <f t="array" aca="1" ref="G57" ca="1">IF(C57&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C57&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H57" cm="1">
+        <f t="array" aca="1" ref="H57" ca="1">IF(D57&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D57&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I57" cm="1">
+        <f t="array" aca="1" ref="I57" ca="1">IF(E57&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E57&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J57" cm="1">
+        <f t="array" aca="1" ref="J57" ca="1">IF(F57&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F57&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1967,12 +2642,24 @@
       <c r="F58" s="3">
         <v>50</v>
       </c>
-      <c r="G58" t="str">
-        <f>IF(C58&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G58" cm="1">
+        <f t="array" aca="1" ref="G58" ca="1">IF(C58&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C58&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H58" cm="1">
+        <f t="array" aca="1" ref="H58" ca="1">IF(D58&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D58&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I58" cm="1">
+        <f t="array" aca="1" ref="I58" ca="1">IF(E58&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E58&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J58" cm="1">
+        <f t="array" aca="1" ref="J58" ca="1">IF(F58&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F58&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1991,12 +2678,24 @@
       <c r="F59" s="3">
         <v>1773</v>
       </c>
-      <c r="G59" t="str">
-        <f>IF(C59&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G59" cm="1">
+        <f t="array" aca="1" ref="G59" ca="1">IF(C59&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C59&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H59" cm="1">
+        <f t="array" aca="1" ref="H59" ca="1">IF(D59&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D59&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I59" cm="1">
+        <f t="array" aca="1" ref="I59" ca="1">IF(E59&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E59&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J59" cm="1">
+        <f t="array" aca="1" ref="J59" ca="1">IF(F59&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F59&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2015,12 +2714,24 @@
       <c r="F60" s="3">
         <v>2248</v>
       </c>
-      <c r="G60" t="str">
-        <f>IF(C60&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G60" cm="1">
+        <f t="array" aca="1" ref="G60" ca="1">IF(C60&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C60&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H60" cm="1">
+        <f t="array" aca="1" ref="H60" ca="1">IF(D60&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D60&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I60" cm="1">
+        <f t="array" aca="1" ref="I60" ca="1">IF(E60&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E60&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J60" cm="1">
+        <f t="array" aca="1" ref="J60" ca="1">IF(F60&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F60&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2039,12 +2750,24 @@
       <c r="F61" s="3">
         <v>1640</v>
       </c>
-      <c r="G61" t="str">
-        <f>IF(C61&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G61" cm="1">
+        <f t="array" aca="1" ref="G61" ca="1">IF(C61&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C61&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H61" cm="1">
+        <f t="array" aca="1" ref="H61" ca="1">IF(D61&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D61&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I61" cm="1">
+        <f t="array" aca="1" ref="I61" ca="1">IF(E61&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E61&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J61" cm="1">
+        <f t="array" aca="1" ref="J61" ca="1">IF(F61&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F61&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2063,12 +2786,24 @@
       <c r="F62" s="3">
         <v>18</v>
       </c>
-      <c r="G62" t="str">
-        <f>IF(C62&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G62" cm="1">
+        <f t="array" aca="1" ref="G62" ca="1">IF(C62&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C62&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H62" cm="1">
+        <f t="array" aca="1" ref="H62" ca="1">IF(D62&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D62&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I62" cm="1">
+        <f t="array" aca="1" ref="I62" ca="1">IF(E62&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E62&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J62" cm="1">
+        <f t="array" aca="1" ref="J62" ca="1">IF(F62&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F62&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2087,12 +2822,24 @@
       <c r="F63" s="3">
         <v>1784</v>
       </c>
-      <c r="G63" t="str">
-        <f>IF(C63&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G63" cm="1">
+        <f t="array" aca="1" ref="G63" ca="1">IF(C63&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C63&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H63" cm="1">
+        <f t="array" aca="1" ref="H63" ca="1">IF(D63&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D63&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I63" cm="1">
+        <f t="array" aca="1" ref="I63" ca="1">IF(E63&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E63&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J63" cm="1">
+        <f t="array" aca="1" ref="J63" ca="1">IF(F63&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F63&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2111,12 +2858,24 @@
       <c r="F64" s="3">
         <v>1506</v>
       </c>
-      <c r="G64" t="str">
-        <f>IF(C64&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G64" cm="1">
+        <f t="array" aca="1" ref="G64" ca="1">IF(C64&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C64&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H64" cm="1">
+        <f t="array" aca="1" ref="H64" ca="1">IF(D64&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D64&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I64" cm="1">
+        <f t="array" aca="1" ref="I64" ca="1">IF(E64&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E64&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J64" cm="1">
+        <f t="array" aca="1" ref="J64" ca="1">IF(F64&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F64&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2135,12 +2894,24 @@
       <c r="F65" s="3">
         <v>1924</v>
       </c>
-      <c r="G65" t="str">
-        <f>IF(C65&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G65" cm="1">
+        <f t="array" aca="1" ref="G65" ca="1">IF(C65&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C65&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H65" cm="1">
+        <f t="array" aca="1" ref="H65" ca="1">IF(D65&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D65&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I65" cm="1">
+        <f t="array" aca="1" ref="I65" ca="1">IF(E65&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E65&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J65" cm="1">
+        <f t="array" aca="1" ref="J65" ca="1">IF(F65&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F65&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2159,12 +2930,24 @@
       <c r="F66" s="3">
         <v>189</v>
       </c>
-      <c r="G66" t="str">
-        <f>IF(C66&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G66" cm="1">
+        <f t="array" aca="1" ref="G66" ca="1">IF(C66&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C66&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H66" cm="1">
+        <f t="array" aca="1" ref="H66" ca="1">IF(D66&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D66&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I66" cm="1">
+        <f t="array" aca="1" ref="I66" ca="1">IF(E66&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E66&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J66" cm="1">
+        <f t="array" aca="1" ref="J66" ca="1">IF(F66&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F66&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2183,12 +2966,24 @@
       <c r="F67" s="3">
         <v>245</v>
       </c>
-      <c r="G67" t="str">
-        <f>IF(C67&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G67" cm="1">
+        <f t="array" aca="1" ref="G67" ca="1">IF(C67&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C67&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H67" cm="1">
+        <f t="array" aca="1" ref="H67" ca="1">IF(D67&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D67&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I67" cm="1">
+        <f t="array" aca="1" ref="I67" ca="1">IF(E67&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E67&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J67" cm="1">
+        <f t="array" aca="1" ref="J67" ca="1">IF(F67&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F67&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2207,12 +3002,24 @@
       <c r="F68" s="3">
         <v>466</v>
       </c>
-      <c r="G68" t="str">
-        <f>IF(C68&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G68" cm="1">
+        <f t="array" aca="1" ref="G68" ca="1">IF(C68&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C68&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H68" cm="1">
+        <f t="array" aca="1" ref="H68" ca="1">IF(D68&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D68&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I68" cm="1">
+        <f t="array" aca="1" ref="I68" ca="1">IF(E68&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E68&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J68" cm="1">
+        <f t="array" aca="1" ref="J68" ca="1">IF(F68&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F68&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2231,12 +3038,24 @@
       <c r="F69" s="3">
         <v>1892</v>
       </c>
-      <c r="G69" t="str">
-        <f>IF(C69&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G69" cm="1">
+        <f t="array" aca="1" ref="G69" ca="1">IF(C69&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C69&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H69" cm="1">
+        <f t="array" aca="1" ref="H69" ca="1">IF(D69&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D69&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I69" cm="1">
+        <f t="array" aca="1" ref="I69" ca="1">IF(E69&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E69&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J69" cm="1">
+        <f t="array" aca="1" ref="J69" ca="1">IF(F69&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F69&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2255,12 +3074,24 @@
       <c r="F70" s="3">
         <v>928</v>
       </c>
-      <c r="G70" t="str">
-        <f>IF(C70&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G70" cm="1">
+        <f t="array" aca="1" ref="G70" ca="1">IF(C70&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C70&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H70" cm="1">
+        <f t="array" aca="1" ref="H70" ca="1">IF(D70&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D70&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="I70" cm="1">
+        <f t="array" aca="1" ref="I70" ca="1">IF(E70&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E70&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J70" cm="1">
+        <f t="array" aca="1" ref="J70" ca="1">IF(F70&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F70&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2279,12 +3110,24 @@
       <c r="F71" s="3">
         <v>333</v>
       </c>
-      <c r="G71" t="str">
-        <f>IF(C71&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G71" cm="1">
+        <f t="array" aca="1" ref="G71" ca="1">IF(C71&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C71&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H71" cm="1">
+        <f t="array" aca="1" ref="H71" ca="1">IF(D71&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D71&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I71" cm="1">
+        <f t="array" aca="1" ref="I71" ca="1">IF(E71&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E71&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J71" cm="1">
+        <f t="array" aca="1" ref="J71" ca="1">IF(F71&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F71&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2303,12 +3146,24 @@
       <c r="F72" s="3">
         <v>1585</v>
       </c>
-      <c r="G72" t="str">
-        <f>IF(C72&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G72" cm="1">
+        <f t="array" aca="1" ref="G72" ca="1">IF(C72&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C72&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H72" cm="1">
+        <f t="array" aca="1" ref="H72" ca="1">IF(D72&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D72&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I72" cm="1">
+        <f t="array" aca="1" ref="I72" ca="1">IF(E72&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E72&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J72" cm="1">
+        <f t="array" aca="1" ref="J72" ca="1">IF(F72&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F72&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2327,12 +3182,24 @@
       <c r="F73" s="3">
         <v>2154</v>
       </c>
-      <c r="G73" t="str">
-        <f>IF(C73&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G73" cm="1">
+        <f t="array" aca="1" ref="G73" ca="1">IF(C73&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C73&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H73" cm="1">
+        <f t="array" aca="1" ref="H73" ca="1">IF(D73&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D73&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I73" cm="1">
+        <f t="array" aca="1" ref="I73" ca="1">IF(E73&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E73&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J73" cm="1">
+        <f t="array" aca="1" ref="J73" ca="1">IF(F73&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F73&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2351,12 +3218,24 @@
       <c r="F74" s="3">
         <v>1522</v>
       </c>
-      <c r="G74" t="str">
-        <f>IF(C74&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G74" cm="1">
+        <f t="array" aca="1" ref="G74" ca="1">IF(C74&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C74&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H74" cm="1">
+        <f t="array" aca="1" ref="H74" ca="1">IF(D74&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D74&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I74" cm="1">
+        <f t="array" aca="1" ref="I74" ca="1">IF(E74&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E74&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J74" cm="1">
+        <f t="array" aca="1" ref="J74" ca="1">IF(F74&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F74&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2375,12 +3254,24 @@
       <c r="F75" s="3">
         <v>149</v>
       </c>
-      <c r="G75" t="str">
-        <f>IF(C75&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G75" cm="1">
+        <f t="array" aca="1" ref="G75" ca="1">IF(C75&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C75&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H75" cm="1">
+        <f t="array" aca="1" ref="H75" ca="1">IF(D75&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D75&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I75" cm="1">
+        <f t="array" aca="1" ref="I75" ca="1">IF(E75&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E75&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J75" cm="1">
+        <f t="array" aca="1" ref="J75" ca="1">IF(F75&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F75&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2399,12 +3290,24 @@
       <c r="F76" s="3">
         <v>1744</v>
       </c>
-      <c r="G76" t="str">
-        <f>IF(C76&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G76" cm="1">
+        <f t="array" aca="1" ref="G76" ca="1">IF(C76&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C76&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H76" cm="1">
+        <f t="array" aca="1" ref="H76" ca="1">IF(D76&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D76&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I76" cm="1">
+        <f t="array" aca="1" ref="I76" ca="1">IF(E76&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E76&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J76" cm="1">
+        <f t="array" aca="1" ref="J76" ca="1">IF(F76&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F76&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2423,12 +3326,24 @@
       <c r="F77" s="3">
         <v>1859</v>
       </c>
-      <c r="G77" t="str">
-        <f>IF(C77&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G77" cm="1">
+        <f t="array" aca="1" ref="G77" ca="1">IF(C77&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C77&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H77" cm="1">
+        <f t="array" aca="1" ref="H77" ca="1">IF(D77&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D77&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I77" cm="1">
+        <f t="array" aca="1" ref="I77" ca="1">IF(E77&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E77&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J77" cm="1">
+        <f t="array" aca="1" ref="J77" ca="1">IF(F77&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F77&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2447,12 +3362,24 @@
       <c r="F78" s="3">
         <v>1684</v>
       </c>
-      <c r="G78" t="str">
-        <f>IF(C78&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G78" cm="1">
+        <f t="array" aca="1" ref="G78" ca="1">IF(C78&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C78&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H78" cm="1">
+        <f t="array" aca="1" ref="H78" ca="1">IF(D78&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D78&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I78" cm="1">
+        <f t="array" aca="1" ref="I78" ca="1">IF(E78&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E78&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J78" cm="1">
+        <f t="array" aca="1" ref="J78" ca="1">IF(F78&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F78&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2471,12 +3398,24 @@
       <c r="F79" s="3">
         <v>1187</v>
       </c>
-      <c r="G79" t="str">
-        <f>IF(C79&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G79" cm="1">
+        <f t="array" aca="1" ref="G79" ca="1">IF(C79&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C79&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H79" cm="1">
+        <f t="array" aca="1" ref="H79" ca="1">IF(D79&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D79&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I79" cm="1">
+        <f t="array" aca="1" ref="I79" ca="1">IF(E79&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E79&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J79" cm="1">
+        <f t="array" aca="1" ref="J79" ca="1">IF(F79&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F79&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2495,12 +3434,24 @@
       <c r="F80" s="3">
         <v>81</v>
       </c>
-      <c r="G80" t="str">
-        <f>IF(C80&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G80" cm="1">
+        <f t="array" aca="1" ref="G80" ca="1">IF(C80&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C80&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H80" cm="1">
+        <f t="array" aca="1" ref="H80" ca="1">IF(D80&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D80&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I80" cm="1">
+        <f t="array" aca="1" ref="I80" ca="1">IF(E80&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E80&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J80" cm="1">
+        <f t="array" aca="1" ref="J80" ca="1">IF(F80&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F80&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2519,12 +3470,24 @@
       <c r="F81" s="3">
         <v>729</v>
       </c>
-      <c r="G81" t="str">
-        <f>IF(C81&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G81" cm="1">
+        <f t="array" aca="1" ref="G81" ca="1">IF(C81&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C81&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H81" cm="1">
+        <f t="array" aca="1" ref="H81" ca="1">IF(D81&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D81&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I81" cm="1">
+        <f t="array" aca="1" ref="I81" ca="1">IF(E81&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E81&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J81" cm="1">
+        <f t="array" aca="1" ref="J81" ca="1">IF(F81&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F81&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2543,12 +3506,24 @@
       <c r="F82" s="3">
         <v>231</v>
       </c>
-      <c r="G82" t="str">
-        <f>IF(C82&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G82" cm="1">
+        <f t="array" aca="1" ref="G82" ca="1">IF(C82&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C82&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H82" cm="1">
+        <f t="array" aca="1" ref="H82" ca="1">IF(D82&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D82&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I82" cm="1">
+        <f t="array" aca="1" ref="I82" ca="1">IF(E82&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E82&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J82" cm="1">
+        <f t="array" aca="1" ref="J82" ca="1">IF(F82&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F82&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2567,12 +3542,24 @@
       <c r="F83" s="3">
         <v>1727</v>
       </c>
-      <c r="G83" t="str">
-        <f>IF(C83&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G83" cm="1">
+        <f t="array" aca="1" ref="G83" ca="1">IF(C83&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C83&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H83" cm="1">
+        <f t="array" aca="1" ref="H83" ca="1">IF(D83&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D83&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I83" cm="1">
+        <f t="array" aca="1" ref="I83" ca="1">IF(E83&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E83&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J83" cm="1">
+        <f t="array" aca="1" ref="J83" ca="1">IF(F83&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F83&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2591,12 +3578,24 @@
       <c r="F84" s="3">
         <v>2018</v>
       </c>
-      <c r="G84" t="str">
-        <f>IF(C84&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G84" cm="1">
+        <f t="array" aca="1" ref="G84" ca="1">IF(C84&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C84&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H84" cm="1">
+        <f t="array" aca="1" ref="H84" ca="1">IF(D84&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D84&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I84" cm="1">
+        <f t="array" aca="1" ref="I84" ca="1">IF(E84&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E84&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J84" cm="1">
+        <f t="array" aca="1" ref="J84" ca="1">IF(F84&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F84&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2615,12 +3614,24 @@
       <c r="F85" s="3">
         <v>605</v>
       </c>
-      <c r="G85" t="str">
-        <f>IF(C85&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G85" cm="1">
+        <f t="array" aca="1" ref="G85" ca="1">IF(C85&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C85&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H85" cm="1">
+        <f t="array" aca="1" ref="H85" ca="1">IF(D85&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D85&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I85" cm="1">
+        <f t="array" aca="1" ref="I85" ca="1">IF(E85&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E85&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J85" cm="1">
+        <f t="array" aca="1" ref="J85" ca="1">IF(F85&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F85&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2639,12 +3650,24 @@
       <c r="F86" s="3">
         <v>1517</v>
       </c>
-      <c r="G86" t="str">
-        <f>IF(C86&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G86" cm="1">
+        <f t="array" aca="1" ref="G86" ca="1">IF(C86&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C86&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H86" cm="1">
+        <f t="array" aca="1" ref="H86" ca="1">IF(D86&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D86&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I86" cm="1">
+        <f t="array" aca="1" ref="I86" ca="1">IF(E86&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E86&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J86" cm="1">
+        <f t="array" aca="1" ref="J86" ca="1">IF(F86&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F86&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2663,12 +3686,24 @@
       <c r="F87" s="3">
         <v>2265</v>
       </c>
-      <c r="G87" t="str">
-        <f>IF(C87&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G87" cm="1">
+        <f t="array" aca="1" ref="G87" ca="1">IF(C87&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C87&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H87" cm="1">
+        <f t="array" aca="1" ref="H87" ca="1">IF(D87&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D87&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I87" cm="1">
+        <f t="array" aca="1" ref="I87" ca="1">IF(E87&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E87&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J87" cm="1">
+        <f t="array" aca="1" ref="J87" ca="1">IF(F87&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F87&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2687,12 +3722,24 @@
       <c r="F88" s="3">
         <v>1062</v>
       </c>
-      <c r="G88" t="str">
-        <f>IF(C88&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G88" cm="1">
+        <f t="array" aca="1" ref="G88" ca="1">IF(C88&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C88&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H88" cm="1">
+        <f t="array" aca="1" ref="H88" ca="1">IF(D88&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D88&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I88" cm="1">
+        <f t="array" aca="1" ref="I88" ca="1">IF(E88&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E88&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J88" cm="1">
+        <f t="array" aca="1" ref="J88" ca="1">IF(F88&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F88&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2711,12 +3758,24 @@
       <c r="F89" s="3">
         <v>807</v>
       </c>
-      <c r="G89" t="str">
-        <f>IF(C89&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G89" cm="1">
+        <f t="array" aca="1" ref="G89" ca="1">IF(C89&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C89&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H89" cm="1">
+        <f t="array" aca="1" ref="H89" ca="1">IF(D89&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D89&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I89" cm="1">
+        <f t="array" aca="1" ref="I89" ca="1">IF(E89&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E89&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J89" cm="1">
+        <f t="array" aca="1" ref="J89" ca="1">IF(F89&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F89&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2735,12 +3794,24 @@
       <c r="F90" s="3">
         <v>870</v>
       </c>
-      <c r="G90" t="str">
-        <f>IF(C90&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G90" cm="1">
+        <f t="array" aca="1" ref="G90" ca="1">IF(C90&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C90&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H90" cm="1">
+        <f t="array" aca="1" ref="H90" ca="1">IF(D90&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D90&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I90" cm="1">
+        <f t="array" aca="1" ref="I90" ca="1">IF(E90&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E90&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J90" cm="1">
+        <f t="array" aca="1" ref="J90" ca="1">IF(F90&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F90&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2759,12 +3830,24 @@
       <c r="F91" s="3">
         <v>1076</v>
       </c>
-      <c r="G91" t="str">
-        <f>IF(C91&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G91" cm="1">
+        <f t="array" aca="1" ref="G91" ca="1">IF(C91&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C91&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H91" cm="1">
+        <f t="array" aca="1" ref="H91" ca="1">IF(D91&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D91&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I91" cm="1">
+        <f t="array" aca="1" ref="I91" ca="1">IF(E91&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E91&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J91" cm="1">
+        <f t="array" aca="1" ref="J91" ca="1">IF(F91&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F91&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2783,12 +3866,24 @@
       <c r="F92" s="3">
         <v>1747</v>
       </c>
-      <c r="G92" t="str">
-        <f>IF(C92&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G92" cm="1">
+        <f t="array" aca="1" ref="G92" ca="1">IF(C92&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C92&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H92" cm="1">
+        <f t="array" aca="1" ref="H92" ca="1">IF(D92&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D92&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I92" cm="1">
+        <f t="array" aca="1" ref="I92" ca="1">IF(E92&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E92&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J92" cm="1">
+        <f t="array" aca="1" ref="J92" ca="1">IF(F92&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F92&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2807,12 +3902,24 @@
       <c r="F93" s="3">
         <v>1156</v>
       </c>
-      <c r="G93" t="str">
-        <f>IF(C93&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G93" cm="1">
+        <f t="array" aca="1" ref="G93" ca="1">IF(C93&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C93&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H93" cm="1">
+        <f t="array" aca="1" ref="H93" ca="1">IF(D93&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D93&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I93" cm="1">
+        <f t="array" aca="1" ref="I93" ca="1">IF(E93&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E93&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J93" cm="1">
+        <f t="array" aca="1" ref="J93" ca="1">IF(F93&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F93&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2831,12 +3938,24 @@
       <c r="F94" s="3">
         <v>271</v>
       </c>
-      <c r="G94" t="str">
-        <f>IF(C94&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G94" cm="1">
+        <f t="array" aca="1" ref="G94" ca="1">IF(C94&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C94&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H94" cm="1">
+        <f t="array" aca="1" ref="H94" ca="1">IF(D94&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D94&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I94" cm="1">
+        <f t="array" aca="1" ref="I94" ca="1">IF(E94&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E94&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J94" cm="1">
+        <f t="array" aca="1" ref="J94" ca="1">IF(F94&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F94&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2855,12 +3974,24 @@
       <c r="F95" s="3">
         <v>2156</v>
       </c>
-      <c r="G95" t="str">
-        <f>IF(C95&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G95" cm="1">
+        <f t="array" aca="1" ref="G95" ca="1">IF(C95&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C95&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H95" cm="1">
+        <f t="array" aca="1" ref="H95" ca="1">IF(D95&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D95&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I95" cm="1">
+        <f t="array" aca="1" ref="I95" ca="1">IF(E95&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E95&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J95" cm="1">
+        <f t="array" aca="1" ref="J95" ca="1">IF(F95&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F95&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2879,12 +4010,24 @@
       <c r="F96" s="3">
         <v>1090</v>
       </c>
-      <c r="G96" t="str">
-        <f>IF(C96&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G96" cm="1">
+        <f t="array" aca="1" ref="G96" ca="1">IF(C96&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C96&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H96" cm="1">
+        <f t="array" aca="1" ref="H96" ca="1">IF(D96&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D96&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I96" cm="1">
+        <f t="array" aca="1" ref="I96" ca="1">IF(E96&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E96&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J96" cm="1">
+        <f t="array" aca="1" ref="J96" ca="1">IF(F96&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F96&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2903,12 +4046,24 @@
       <c r="F97" s="3">
         <v>2115</v>
       </c>
-      <c r="G97" t="str">
-        <f>IF(C97&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G97" cm="1">
+        <f t="array" aca="1" ref="G97" ca="1">IF(C97&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C97&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="H97" cm="1">
+        <f t="array" aca="1" ref="H97" ca="1">IF(D97&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D97&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I97" cm="1">
+        <f t="array" aca="1" ref="I97" ca="1">IF(E97&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E97&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J97" cm="1">
+        <f t="array" aca="1" ref="J97" ca="1">IF(F97&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F97&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2927,12 +4082,24 @@
       <c r="F98" s="3">
         <v>1410</v>
       </c>
-      <c r="G98" t="str">
-        <f>IF(C98&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G98" cm="1">
+        <f t="array" aca="1" ref="G98" ca="1">IF(C98&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C98&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H98" cm="1">
+        <f t="array" aca="1" ref="H98" ca="1">IF(D98&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D98&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I98" cm="1">
+        <f t="array" aca="1" ref="I98" ca="1">IF(E98&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E98&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="J98" cm="1">
+        <f t="array" aca="1" ref="J98" ca="1">IF(F98&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F98&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2951,12 +4118,24 @@
       <c r="F99" s="3">
         <v>1579</v>
       </c>
-      <c r="G99" t="str">
-        <f>IF(C99&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G99" cm="1">
+        <f t="array" aca="1" ref="G99" ca="1">IF(C99&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C99&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H99" cm="1">
+        <f t="array" aca="1" ref="H99" ca="1">IF(D99&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D99&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I99" cm="1">
+        <f t="array" aca="1" ref="I99" ca="1">IF(E99&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E99&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J99" cm="1">
+        <f t="array" aca="1" ref="J99" ca="1">IF(F99&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F99&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2975,12 +4154,24 @@
       <c r="F100" s="3">
         <v>2064</v>
       </c>
-      <c r="G100" t="str">
-        <f>IF(C100&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G100" cm="1">
+        <f t="array" aca="1" ref="G100" ca="1">IF(C100&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C100&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H100" cm="1">
+        <f t="array" aca="1" ref="H100" ca="1">IF(D100&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D100&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I100" cm="1">
+        <f t="array" aca="1" ref="I100" ca="1">IF(E100&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E100&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>2</v>
+      </c>
+      <c r="J100" cm="1">
+        <f t="array" aca="1" ref="J100" ca="1">IF(F100&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F100&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2999,9 +4190,21 @@
       <c r="F101" s="3">
         <v>1778</v>
       </c>
-      <c r="G101" t="str">
-        <f>IF(C101&gt;=threshold!$B$3,"Alert! Too Warm!","Alert! Too Cold!")</f>
-        <v>Alert! Too Cold!</v>
+      <c r="G101" cm="1">
+        <f t="array" aca="1" ref="G101" ca="1">IF(C101&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$3")),1,IF(C101&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$B$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="H101" cm="1">
+        <f t="array" aca="1" ref="H101" ca="1">IF(D101&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$3")),1,IF(D101&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$C$2")),2,0))</f>
+        <v>0</v>
+      </c>
+      <c r="I101" cm="1">
+        <f t="array" aca="1" ref="I101" ca="1">IF(E101&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$3")),1,IF(E101&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$D$2")),2,0))</f>
+        <v>1</v>
+      </c>
+      <c r="J101" cm="1">
+        <f t="array" aca="1" ref="J101" ca="1">IF(F101&gt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$3")),1,IF(F101&lt;=(INDIRECT("'" &amp; $M$1 &amp; "'!$E$2")),2,0))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
